--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run10/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run10/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,784 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.3938,0.3056,0.0685,0.3982</t>
-  </si>
-  <si>
-    <t>0.0034,0.0014,0.0021,0.9969</t>
-  </si>
-  <si>
-    <t>0.2247,0.2684,0.0034,0.5939</t>
-  </si>
-  <si>
-    <t>0.0440,0.0239,0.0041,0.9765</t>
-  </si>
-  <si>
-    <t>0.9945,0.0021,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9853,0.0088,0.0017,0.0020</t>
-  </si>
-  <si>
-    <t>0.9878,0.0051,0.0009,0.0021</t>
-  </si>
-  <si>
-    <t>0.9943,0.0020,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9923,0.0017,0.0005,0.0021</t>
-  </si>
-  <si>
-    <t>0.9913,0.0061,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9935,0.0021,0.0003,0.0013</t>
-  </si>
-  <si>
-    <t>0.9962,0.0010,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.7246,0.0953,0.1704,0.0344</t>
-  </si>
-  <si>
-    <t>0.3038,0.1244,0.6773,0.0248</t>
-  </si>
-  <si>
-    <t>0.0861,0.1386,0.7971,0.0010</t>
-  </si>
-  <si>
-    <t>0.2532,0.2213,0.5729,0.0431</t>
-  </si>
-  <si>
-    <t>0.6852,0.0458,0.2935,0.0057</t>
-  </si>
-  <si>
-    <t>0.0029,0.9937,0.0033,0.0003</t>
-  </si>
-  <si>
-    <t>0.0063,0.9897,0.0073,0.0002</t>
-  </si>
-  <si>
-    <t>0.3785,0.6765,0.0214,0.0041</t>
-  </si>
-  <si>
-    <t>0.0336,0.9699,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.9974,0.0026,0.0003</t>
-  </si>
-  <si>
-    <t>0.5493,0.0149,0.5143,0.0080</t>
-  </si>
-  <si>
-    <t>0.4331,0.0176,0.5279,0.0318</t>
-  </si>
-  <si>
-    <t>0.0978,0.0122,0.8752,0.0285</t>
-  </si>
-  <si>
-    <t>0.2538,0.0685,0.4808,0.2664</t>
-  </si>
-  <si>
-    <t>0.1026,0.0173,0.9005,0.0097</t>
-  </si>
-  <si>
-    <t>0.0256,0.0114,0.9564,0.0082</t>
-  </si>
-  <si>
-    <t>0.0143,0.0028,0.9766,0.0054</t>
-  </si>
-  <si>
-    <t>0.2171,0.8142,0.0063,0.0065</t>
-  </si>
-  <si>
-    <t>0.2548,0.0799,0.7569,0.0094</t>
-  </si>
-  <si>
-    <t>0.0070,0.0052,0.9920,0.0009</t>
-  </si>
-  <si>
-    <t>0.0175,0.8677,0.2737,0.0014</t>
-  </si>
-  <si>
-    <t>0.6306,0.2393,0.1833,0.0178</t>
-  </si>
-  <si>
-    <t>0.2128,0.0460,0.8239,0.0037</t>
-  </si>
-  <si>
-    <t>0.6596,0.4438,0.0091,0.0035</t>
-  </si>
-  <si>
-    <t>0.0362,0.9466,0.0538,0.0010</t>
-  </si>
-  <si>
-    <t>0.0680,0.7586,0.3378,0.0311</t>
-  </si>
-  <si>
-    <t>0.0197,0.0570,0.9322,0.0268</t>
-  </si>
-  <si>
-    <t>0.0737,0.1043,0.8767,0.0031</t>
-  </si>
-  <si>
-    <t>0.0103,0.0063,0.8352,0.2709</t>
-  </si>
-  <si>
-    <t>0.0699,0.1409,0.8073,0.0025</t>
-  </si>
-  <si>
-    <t>0.0090,0.9630,0.0640,0.0017</t>
-  </si>
-  <si>
-    <t>0.0397,0.0418,0.9319,0.0213</t>
-  </si>
-  <si>
-    <t>0.1771,0.3239,0.0207,0.7708</t>
-  </si>
-  <si>
-    <t>0.0014,0.9906,0.0025,0.0049</t>
-  </si>
-  <si>
-    <t>0.0113,0.9662,0.0384,0.0008</t>
-  </si>
-  <si>
-    <t>0.0019,0.9898,0.0557,0.0002</t>
-  </si>
-  <si>
-    <t>0.0059,0.0799,0.9666,0.0005</t>
-  </si>
-  <si>
-    <t>0.0046,0.3717,0.9597,0.0006</t>
-  </si>
-  <si>
-    <t>0.3306,0.0263,0.7170,0.0066</t>
-  </si>
-  <si>
-    <t>0.2970,0.0075,0.6990,0.0248</t>
-  </si>
-  <si>
-    <t>0.0041,0.2507,0.9483,0.0043</t>
-  </si>
-  <si>
-    <t>0.0036,0.0147,0.9893,0.0011</t>
-  </si>
-  <si>
-    <t>0.7360,0.4102,0.0031,0.0015</t>
-  </si>
-  <si>
-    <t>0.7953,0.1820,0.0558,0.0168</t>
-  </si>
-  <si>
-    <t>0.9751,0.0150,0.0035,0.0040</t>
-  </si>
-  <si>
-    <t>0.0052,0.1971,0.9824,0.0005</t>
-  </si>
-  <si>
-    <t>0.9902,0.0031,0.0005,0.0029</t>
-  </si>
-  <si>
-    <t>0.9799,0.0118,0.0020,0.0026</t>
-  </si>
-  <si>
-    <t>0.9710,0.0222,0.0035,0.0022</t>
-  </si>
-  <si>
-    <t>0.0037,0.7236,0.9215,0.0009</t>
-  </si>
-  <si>
-    <t>0.0208,0.0242,0.9681,0.0020</t>
-  </si>
-  <si>
-    <t>0.0017,0.0339,0.9869,0.0023</t>
-  </si>
-  <si>
-    <t>0.0010,0.6067,0.9738,0.0002</t>
-  </si>
-  <si>
-    <t>0.0115,0.0044,0.9856,0.0012</t>
-  </si>
-  <si>
-    <t>0.0371,0.8940,0.2213,0.0026</t>
-  </si>
-  <si>
-    <t>0.0064,0.9859,0.0127,0.0002</t>
-  </si>
-  <si>
-    <t>0.8720,0.0646,0.0582,0.0042</t>
-  </si>
-  <si>
-    <t>0.6247,0.2432,0.1942,0.0133</t>
-  </si>
-  <si>
-    <t>0.0182,0.0360,0.9761,0.0021</t>
-  </si>
-  <si>
-    <t>0.0011,0.7226,0.9447,0.0000</t>
-  </si>
-  <si>
-    <t>0.0168,0.4390,0.8659,0.0032</t>
-  </si>
-  <si>
-    <t>0.0016,0.9650,0.5327,0.0006</t>
-  </si>
-  <si>
-    <t>0.0023,0.9231,0.7492,0.0006</t>
-  </si>
-  <si>
-    <t>0.1827,0.0027,0.0270,0.8083</t>
-  </si>
-  <si>
-    <t>0.0060,0.0063,0.0051,0.9933</t>
-  </si>
-  <si>
-    <t>0.0031,0.0507,0.0009,0.9948</t>
-  </si>
-  <si>
-    <t>0.0147,0.0045,0.0013,0.9922</t>
-  </si>
-  <si>
-    <t>0.0080,0.0030,0.0127,0.9883</t>
-  </si>
-  <si>
-    <t>0.0016,0.0014,0.0013,0.9981</t>
-  </si>
-  <si>
-    <t>0.0013,0.9613,0.7867,0.0003</t>
-  </si>
-  <si>
-    <t>0.0010,0.9283,0.8705,0.0001</t>
-  </si>
-  <si>
-    <t>0.0799,0.5083,0.5342,0.0044</t>
-  </si>
-  <si>
-    <t>0.0038,0.5080,0.9388,0.0004</t>
-  </si>
-  <si>
-    <t>0.0004,0.9713,0.7426,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.8536,0.8641,0.0003</t>
-  </si>
-  <si>
-    <t>0.9840,0.0057,0.0022,0.0032</t>
-  </si>
-  <si>
-    <t>0.9566,0.0537,0.0021,0.0016</t>
-  </si>
-  <si>
-    <t>0.9781,0.0179,0.0034,0.0019</t>
-  </si>
-  <si>
-    <t>0.9881,0.0066,0.0010,0.0015</t>
-  </si>
-  <si>
-    <t>0.9759,0.0131,0.0014,0.0047</t>
-  </si>
-  <si>
-    <t>0.9684,0.0392,0.0037,0.0014</t>
-  </si>
-  <si>
-    <t>0.9706,0.0403,0.0015,0.0012</t>
-  </si>
-  <si>
-    <t>0.9834,0.0104,0.0015,0.0017</t>
-  </si>
-  <si>
-    <t>0.9929,0.0005,0.0001,0.0039</t>
-  </si>
-  <si>
-    <t>0.9911,0.0029,0.0017,0.0018</t>
-  </si>
-  <si>
-    <t>0.9890,0.0079,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9975,0.0008,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9826,0.0101,0.0026,0.0031</t>
-  </si>
-  <si>
-    <t>0.9783,0.0181,0.0030,0.0014</t>
-  </si>
-  <si>
-    <t>0.9899,0.0035,0.0016,0.0013</t>
-  </si>
-  <si>
-    <t>0.9937,0.0008,0.0001,0.0023</t>
-  </si>
-  <si>
-    <t>0.0109,0.0019,0.9854,0.0025</t>
-  </si>
-  <si>
-    <t>0.0700,0.0551,0.8820,0.0089</t>
-  </si>
-  <si>
-    <t>0.6062,0.0189,0.1214,0.1726</t>
-  </si>
-  <si>
-    <t>0.2763,0.0083,0.7846,0.0104</t>
-  </si>
-  <si>
-    <t>0.1363,0.8815,0.0074,0.0024</t>
-  </si>
-  <si>
-    <t>0.0173,0.9743,0.0114,0.0015</t>
-  </si>
-  <si>
-    <t>0.0354,0.9632,0.0008,0.0015</t>
-  </si>
-  <si>
-    <t>0.3772,0.6530,0.0416,0.0027</t>
-  </si>
-  <si>
-    <t>0.0294,0.9630,0.0068,0.0015</t>
-  </si>
-  <si>
-    <t>0.0037,0.9907,0.0027,0.0009</t>
-  </si>
-  <si>
-    <t>0.8688,0.1724,0.0060,0.0030</t>
-  </si>
-  <si>
-    <t>0.7005,0.0737,0.2513,0.0355</t>
-  </si>
-  <si>
-    <t>0.1897,0.0295,0.8316,0.0060</t>
-  </si>
-  <si>
-    <t>0.2379,0.4918,0.2390,0.3591</t>
-  </si>
-  <si>
-    <t>0.5914,0.2807,0.1471,0.0752</t>
-  </si>
-  <si>
-    <t>0.0807,0.2803,0.0319,0.9023</t>
-  </si>
-  <si>
-    <t>0.0006,0.9965,0.0033,0.0005</t>
-  </si>
-  <si>
-    <t>0.0073,0.9652,0.1209,0.0021</t>
-  </si>
-  <si>
-    <t>0.0095,0.9682,0.0091,0.0333</t>
-  </si>
-  <si>
-    <t>0.0005,0.9441,0.9102,0.0001</t>
-  </si>
-  <si>
-    <t>0.0068,0.9777,0.0889,0.0007</t>
-  </si>
-  <si>
-    <t>0.7551,0.2440,0.0534,0.0047</t>
-  </si>
-  <si>
-    <t>0.7275,0.3446,0.0149,0.0015</t>
-  </si>
-  <si>
-    <t>0.9840,0.0061,0.0024,0.0033</t>
-  </si>
-  <si>
-    <t>0.9823,0.0090,0.0012,0.0022</t>
-  </si>
-  <si>
-    <t>0.9834,0.0098,0.0014,0.0026</t>
-  </si>
-  <si>
-    <t>0.9885,0.0033,0.0007,0.0019</t>
-  </si>
-  <si>
-    <t>0.9824,0.0074,0.0018,0.0023</t>
-  </si>
-  <si>
-    <t>0.9282,0.0713,0.0147,0.0058</t>
-  </si>
-  <si>
-    <t>0.9539,0.0229,0.0067,0.0116</t>
-  </si>
-  <si>
-    <t>0.9872,0.0046,0.0014,0.0013</t>
-  </si>
-  <si>
-    <t>0.0022,0.7617,0.9010,0.0003</t>
-  </si>
-  <si>
-    <t>0.0067,0.7814,0.8225,0.0010</t>
-  </si>
-  <si>
-    <t>0.0047,0.1323,0.9741,0.0013</t>
-  </si>
-  <si>
-    <t>0.0156,0.3095,0.7890,0.0010</t>
-  </si>
-  <si>
-    <t>0.3184,0.3805,0.3852,0.3323</t>
-  </si>
-  <si>
-    <t>0.6590,0.1540,0.2356,0.0157</t>
-  </si>
-  <si>
-    <t>0.3276,0.0104,0.7616,0.0089</t>
-  </si>
-  <si>
-    <t>0.6620,0.0799,0.2545,0.0561</t>
-  </si>
-  <si>
-    <t>0.1067,0.0131,0.0162,0.9281</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0026,0.9992</t>
-  </si>
-  <si>
-    <t>0.0010,0.0141,0.0003,0.9987</t>
-  </si>
-  <si>
-    <t>0.0047,0.0017,0.0017,0.9964</t>
-  </si>
-  <si>
-    <t>0.0016,0.9144,0.8127,0.0006</t>
-  </si>
-  <si>
-    <t>0.9681,0.0115,0.0053,0.0063</t>
-  </si>
-  <si>
-    <t>0.0485,0.9395,0.0053,0.0040</t>
-  </si>
-  <si>
-    <t>0.9561,0.0192,0.0068,0.0087</t>
-  </si>
-  <si>
-    <t>0.5771,0.5267,0.0081,0.0033</t>
-  </si>
-  <si>
-    <t>0.9385,0.0123,0.0042,0.0296</t>
-  </si>
-  <si>
-    <t>0.4158,0.0101,0.0209,0.6547</t>
-  </si>
-  <si>
-    <t>0.9714,0.0085,0.0011,0.0085</t>
-  </si>
-  <si>
-    <t>0.0009,0.0273,0.9920,0.0029</t>
-  </si>
-  <si>
-    <t>0.3972,0.0009,0.0024,0.7813</t>
-  </si>
-  <si>
-    <t>0.8849,0.0093,0.0062,0.0798</t>
-  </si>
-  <si>
-    <t>0.8055,0.1583,0.0608,0.0081</t>
-  </si>
-  <si>
-    <t>0.8239,0.1316,0.0256,0.0120</t>
-  </si>
-  <si>
-    <t>0.9066,0.0842,0.0220,0.0024</t>
-  </si>
-  <si>
-    <t>0.4101,0.3211,0.2685,0.0192</t>
-  </si>
-  <si>
-    <t>0.5671,0.4198,0.0897,0.0132</t>
-  </si>
-  <si>
-    <t>0.6558,0.4199,0.0124,0.0023</t>
-  </si>
-  <si>
-    <t>0.9885,0.0034,0.0012,0.0020</t>
-  </si>
-  <si>
-    <t>0.9837,0.0051,0.0016,0.0034</t>
-  </si>
-  <si>
-    <t>0.9932,0.0010,0.0005,0.0021</t>
-  </si>
-  <si>
-    <t>0.9584,0.0017,0.0018,0.0384</t>
-  </si>
-  <si>
-    <t>0.9906,0.0012,0.0007,0.0027</t>
-  </si>
-  <si>
-    <t>0.9695,0.0289,0.0021,0.0019</t>
-  </si>
-  <si>
-    <t>0.9791,0.0083,0.0017,0.0045</t>
-  </si>
-  <si>
-    <t>0.9859,0.0084,0.0012,0.0014</t>
-  </si>
-  <si>
-    <t>0.6853,0.4073,0.0095,0.0024</t>
-  </si>
-  <si>
-    <t>0.7657,0.3188,0.0112,0.0011</t>
-  </si>
-  <si>
-    <t>0.5767,0.5622,0.0044,0.0014</t>
-  </si>
-  <si>
-    <t>0.9362,0.0541,0.0133,0.0056</t>
-  </si>
-  <si>
-    <t>0.5492,0.6187,0.0021,0.0011</t>
-  </si>
-  <si>
-    <t>0.9302,0.0365,0.0148,0.0135</t>
-  </si>
-  <si>
-    <t>0.9711,0.0237,0.0033,0.0019</t>
-  </si>
-  <si>
-    <t>0.9013,0.0926,0.0197,0.0045</t>
-  </si>
-  <si>
-    <t>0.0161,0.0890,0.9739,0.0006</t>
-  </si>
-  <si>
-    <t>0.9082,0.0733,0.0292,0.0027</t>
-  </si>
-  <si>
-    <t>0.0026,0.0113,0.9929,0.0007</t>
-  </si>
-  <si>
-    <t>0.0043,0.1020,0.9786,0.0029</t>
-  </si>
-  <si>
-    <t>0.0441,0.0282,0.9538,0.0007</t>
-  </si>
-  <si>
-    <t>0.0038,0.0982,0.9820,0.0005</t>
-  </si>
-  <si>
-    <t>0.0382,0.0200,0.9569,0.0004</t>
-  </si>
-  <si>
-    <t>0.0182,0.0018,0.9884,0.0004</t>
-  </si>
-  <si>
-    <t>0.0360,0.0136,0.9636,0.0014</t>
-  </si>
-  <si>
-    <t>0.3337,0.0939,0.6069,0.0407</t>
-  </si>
-  <si>
-    <t>0.4286,0.3684,0.2681,0.0304</t>
-  </si>
-  <si>
-    <t>0.4816,0.3372,0.2451,0.0127</t>
-  </si>
-  <si>
-    <t>0.3632,0.1144,0.5268,0.0096</t>
-  </si>
-  <si>
-    <t>0.4084,0.0376,0.6335,0.0021</t>
-  </si>
-  <si>
-    <t>0.4762,0.0421,0.4975,0.0025</t>
-  </si>
-  <si>
-    <t>0.5011,0.0112,0.2608,0.1394</t>
-  </si>
-  <si>
-    <t>0.1624,0.7129,0.1867,0.0217</t>
-  </si>
-  <si>
-    <t>0.2522,0.8068,0.0063,0.0005</t>
-  </si>
-  <si>
-    <t>0.0925,0.9336,0.0027,0.0006</t>
-  </si>
-  <si>
-    <t>0.4405,0.7394,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.9716,0.0209,0.0027,0.0033</t>
-  </si>
-  <si>
-    <t>0.8009,0.2447,0.0229,0.0017</t>
-  </si>
-  <si>
-    <t>0.2202,0.6073,0.1026,0.1748</t>
-  </si>
-  <si>
-    <t>0.7242,0.0546,0.2276,0.0156</t>
-  </si>
-  <si>
-    <t>0.4565,0.0275,0.0250,0.5498</t>
-  </si>
-  <si>
-    <t>0.7860,0.0185,0.2022,0.0041</t>
-  </si>
-  <si>
-    <t>0.4349,0.0998,0.3504,0.2509</t>
-  </si>
-  <si>
-    <t>0.0222,0.0076,0.9564,0.0168</t>
-  </si>
-  <si>
-    <t>0.1036,0.1033,0.8345,0.0186</t>
-  </si>
-  <si>
-    <t>0.0760,0.1226,0.8671,0.0140</t>
-  </si>
-  <si>
-    <t>0.0296,0.0515,0.9380,0.0049</t>
-  </si>
-  <si>
-    <t>0.0303,0.0626,0.9373,0.0031</t>
-  </si>
-  <si>
-    <t>0.9842,0.0050,0.0006,0.0043</t>
-  </si>
-  <si>
-    <t>0.9582,0.0362,0.0102,0.0015</t>
-  </si>
-  <si>
-    <t>0.9715,0.0159,0.0020,0.0050</t>
-  </si>
-  <si>
-    <t>0.9766,0.0175,0.0034,0.0023</t>
-  </si>
-  <si>
-    <t>0.9804,0.0255,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.9903,0.0059,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.9900,0.0020,0.0003,0.0033</t>
-  </si>
-  <si>
-    <t>0.9823,0.0073,0.0030,0.0027</t>
-  </si>
-  <si>
-    <t>0.1600,0.0059,0.8969,0.0043</t>
-  </si>
-  <si>
-    <t>0.0685,0.8828,0.0289,0.0375</t>
-  </si>
-  <si>
-    <t>0.8522,0.0439,0.0852,0.0188</t>
-  </si>
-  <si>
-    <t>0.0696,0.0156,0.9393,0.0029</t>
-  </si>
-  <si>
-    <t>0.0006,0.0258,0.9954,0.0005</t>
-  </si>
-  <si>
-    <t>0.1059,0.0620,0.8565,0.0041</t>
-  </si>
-  <si>
-    <t>0.0010,0.0021,0.9978,0.0003</t>
-  </si>
-  <si>
-    <t>0.1184,0.0248,0.8571,0.0168</t>
-  </si>
-  <si>
-    <t>0.0019,0.0058,0.9951,0.0010</t>
-  </si>
-  <si>
-    <t>0.0027,0.0048,0.9454,0.1099</t>
-  </si>
-  <si>
-    <t>0.3405,0.1806,0.4202,0.2368</t>
-  </si>
-  <si>
-    <t>0.5815,0.0801,0.1028,0.2976</t>
-  </si>
-  <si>
-    <t>0.5018,0.0093,0.4784,0.0294</t>
-  </si>
-  <si>
-    <t>0.8405,0.0334,0.0811,0.0345</t>
-  </si>
-  <si>
-    <t>0.9818,0.0155,0.0005,0.0020</t>
-  </si>
-  <si>
-    <t>0.9873,0.0071,0.0014,0.0012</t>
-  </si>
-  <si>
-    <t>0.9958,0.0026,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9719,0.0187,0.0051,0.0026</t>
-  </si>
-  <si>
-    <t>0.9799,0.0134,0.0033,0.0016</t>
-  </si>
-  <si>
-    <t>0.9875,0.0140,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9854,0.0110,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.8821,0.1589,0.0033,0.0058</t>
-  </si>
-  <si>
-    <t>0.1180,0.0769,0.8341,0.0098</t>
-  </si>
-  <si>
-    <t>0.0019,0.0557,0.9842,0.0026</t>
-  </si>
-  <si>
-    <t>0.0168,0.0056,0.9734,0.0068</t>
-  </si>
-  <si>
-    <t>0.1003,0.0089,0.8992,0.0058</t>
-  </si>
-  <si>
-    <t>0.0232,0.0104,0.9619,0.0037</t>
-  </si>
-  <si>
-    <t>0.2221,0.0155,0.4299,0.3243</t>
-  </si>
-  <si>
-    <t>0.2321,0.0514,0.7087,0.0586</t>
-  </si>
-  <si>
-    <t>0.0214,0.0667,0.9272,0.0187</t>
-  </si>
-  <si>
-    <t>0.8043,0.0036,0.0023,0.3003</t>
-  </si>
-  <si>
-    <t>0.0533,0.1228,0.0063,0.9604</t>
-  </si>
-  <si>
-    <t>0.0923,0.0116,0.0006,0.9708</t>
-  </si>
-  <si>
-    <t>0.0054,0.0005,0.0011,0.9965</t>
-  </si>
-  <si>
-    <t>0.0045,0.0013,0.0004,0.9974</t>
-  </si>
-  <si>
-    <t>0.6716,0.1416,0.0300,0.0997</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.7039,0.0073,0.0430,0.2481</t>
+  </si>
+  <si>
+    <t>0.0052,0.0007,0.0006,0.9973</t>
+  </si>
+  <si>
+    <t>0.4028,0.0158,0.0229,0.6837</t>
+  </si>
+  <si>
+    <t>0.0570,0.0426,0.0318,0.9486</t>
+  </si>
+  <si>
+    <t>0.9898,0.0049,0.0005,0.0017</t>
+  </si>
+  <si>
+    <t>0.9913,0.0017,0.0002,0.0028</t>
+  </si>
+  <si>
+    <t>0.9825,0.0092,0.0035,0.0025</t>
+  </si>
+  <si>
+    <t>0.9890,0.0035,0.0011,0.0025</t>
+  </si>
+  <si>
+    <t>0.9822,0.0127,0.0018,0.0019</t>
+  </si>
+  <si>
+    <t>0.9652,0.0307,0.0037,0.0034</t>
+  </si>
+  <si>
+    <t>0.9883,0.0058,0.0009,0.0016</t>
+  </si>
+  <si>
+    <t>0.9929,0.0021,0.0006,0.0016</t>
+  </si>
+  <si>
+    <t>0.5424,0.0482,0.4214,0.0427</t>
+  </si>
+  <si>
+    <t>0.4064,0.0504,0.6130,0.0134</t>
+  </si>
+  <si>
+    <t>0.4065,0.0229,0.6755,0.0042</t>
+  </si>
+  <si>
+    <t>0.2063,0.0842,0.6680,0.0081</t>
+  </si>
+  <si>
+    <t>0.8352,0.0363,0.1156,0.0056</t>
+  </si>
+  <si>
+    <t>0.0041,0.9923,0.0049,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.9954,0.0034,0.0006</t>
+  </si>
+  <si>
+    <t>0.0607,0.9322,0.0077,0.0032</t>
+  </si>
+  <si>
+    <t>0.0312,0.9723,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.0021,0.9962,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.4315,0.0093,0.6030,0.0216</t>
+  </si>
+  <si>
+    <t>0.3382,0.0745,0.6275,0.0049</t>
+  </si>
+  <si>
+    <t>0.1979,0.0059,0.8988,0.0009</t>
+  </si>
+  <si>
+    <t>0.2169,0.0205,0.8293,0.0134</t>
+  </si>
+  <si>
+    <t>0.0984,0.0105,0.9131,0.0050</t>
+  </si>
+  <si>
+    <t>0.1022,0.0090,0.8979,0.0110</t>
+  </si>
+  <si>
+    <t>0.0043,0.0018,0.9920,0.0016</t>
+  </si>
+  <si>
+    <t>0.7493,0.3075,0.0217,0.0021</t>
+  </si>
+  <si>
+    <t>0.2076,0.7031,0.1637,0.0166</t>
+  </si>
+  <si>
+    <t>0.0008,0.0035,0.9928,0.0113</t>
+  </si>
+  <si>
+    <t>0.0052,0.9297,0.4197,0.0005</t>
+  </si>
+  <si>
+    <t>0.7767,0.1977,0.0368,0.0149</t>
+  </si>
+  <si>
+    <t>0.6532,0.1653,0.2056,0.0180</t>
+  </si>
+  <si>
+    <t>0.8888,0.1757,0.0037,0.0010</t>
+  </si>
+  <si>
+    <t>0.0217,0.9509,0.0629,0.0024</t>
+  </si>
+  <si>
+    <t>0.0206,0.7553,0.7225,0.0044</t>
+  </si>
+  <si>
+    <t>0.0100,0.2174,0.9618,0.0015</t>
+  </si>
+  <si>
+    <t>0.0608,0.0549,0.9052,0.0041</t>
+  </si>
+  <si>
+    <t>0.0577,0.0068,0.9052,0.0293</t>
+  </si>
+  <si>
+    <t>0.0552,0.1270,0.9029,0.0034</t>
+  </si>
+  <si>
+    <t>0.0058,0.9657,0.0727,0.0015</t>
+  </si>
+  <si>
+    <t>0.1336,0.0279,0.8801,0.0057</t>
+  </si>
+  <si>
+    <t>0.0705,0.5172,0.0163,0.8710</t>
+  </si>
+  <si>
+    <t>0.0006,0.9921,0.0027,0.0154</t>
+  </si>
+  <si>
+    <t>0.0071,0.9676,0.0999,0.0015</t>
+  </si>
+  <si>
+    <t>0.0074,0.9448,0.2734,0.0085</t>
+  </si>
+  <si>
+    <t>0.0110,0.1159,0.9614,0.0015</t>
+  </si>
+  <si>
+    <t>0.0089,0.0453,0.9842,0.0004</t>
+  </si>
+  <si>
+    <t>0.1080,0.0116,0.8827,0.0137</t>
+  </si>
+  <si>
+    <t>0.0249,0.0022,0.9775,0.0013</t>
+  </si>
+  <si>
+    <t>0.0023,0.0317,0.9884,0.0017</t>
+  </si>
+  <si>
+    <t>0.0487,0.0611,0.9213,0.0049</t>
+  </si>
+  <si>
+    <t>0.8891,0.1309,0.0126,0.0037</t>
+  </si>
+  <si>
+    <t>0.9472,0.0426,0.0121,0.0041</t>
+  </si>
+  <si>
+    <t>0.9730,0.0132,0.0024,0.0050</t>
+  </si>
+  <si>
+    <t>0.0037,0.0103,0.9932,0.0009</t>
+  </si>
+  <si>
+    <t>0.9828,0.0080,0.0008,0.0027</t>
+  </si>
+  <si>
+    <t>0.9168,0.1342,0.0015,0.0017</t>
+  </si>
+  <si>
+    <t>0.9460,0.0895,0.0029,0.0010</t>
+  </si>
+  <si>
+    <t>0.0021,0.7678,0.9543,0.0002</t>
+  </si>
+  <si>
+    <t>0.0084,0.1097,0.9737,0.0025</t>
+  </si>
+  <si>
+    <t>0.0196,0.0143,0.9679,0.0064</t>
+  </si>
+  <si>
+    <t>0.0021,0.4725,0.9775,0.0002</t>
+  </si>
+  <si>
+    <t>0.0095,0.0039,0.9840,0.0015</t>
+  </si>
+  <si>
+    <t>0.0751,0.8930,0.0888,0.0026</t>
+  </si>
+  <si>
+    <t>0.0106,0.9876,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.5494,0.0372,0.5156,0.0060</t>
+  </si>
+  <si>
+    <t>0.4153,0.1623,0.4795,0.0171</t>
+  </si>
+  <si>
+    <t>0.0292,0.0532,0.9637,0.0030</t>
+  </si>
+  <si>
+    <t>0.0016,0.8825,0.8512,0.0001</t>
+  </si>
+  <si>
+    <t>0.0087,0.8328,0.6844,0.0006</t>
+  </si>
+  <si>
+    <t>0.0013,0.9886,0.0689,0.0005</t>
+  </si>
+  <si>
+    <t>0.0012,0.8867,0.9337,0.0002</t>
+  </si>
+  <si>
+    <t>0.0622,0.0012,0.0219,0.9287</t>
+  </si>
+  <si>
+    <t>0.0011,0.0020,0.0007,0.9988</t>
+  </si>
+  <si>
+    <t>0.0105,0.0338,0.0015,0.9909</t>
+  </si>
+  <si>
+    <t>0.0463,0.0303,0.0048,0.9722</t>
+  </si>
+  <si>
+    <t>0.0116,0.0015,0.0051,0.9886</t>
+  </si>
+  <si>
+    <t>0.0043,0.0476,0.0015,0.9935</t>
+  </si>
+  <si>
+    <t>0.0012,0.9727,0.6816,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.4394,0.9705,0.0002</t>
+  </si>
+  <si>
+    <t>0.0063,0.7824,0.8697,0.0008</t>
+  </si>
+  <si>
+    <t>0.0033,0.1857,0.9768,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9627,0.9293,0.0000</t>
+  </si>
+  <si>
+    <t>0.0033,0.7976,0.7362,0.0004</t>
+  </si>
+  <si>
+    <t>0.9901,0.0082,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.9727,0.0290,0.0069,0.0008</t>
+  </si>
+  <si>
+    <t>0.9038,0.1561,0.0040,0.0022</t>
+  </si>
+  <si>
+    <t>0.9899,0.0066,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9860,0.0063,0.0007,0.0026</t>
+  </si>
+  <si>
+    <t>0.9873,0.0058,0.0017,0.0018</t>
+  </si>
+  <si>
+    <t>0.9875,0.0104,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.9594,0.0541,0.0022,0.0018</t>
+  </si>
+  <si>
+    <t>0.9948,0.0013,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9881,0.0070,0.0024,0.0013</t>
+  </si>
+  <si>
+    <t>0.9956,0.0012,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9956,0.0021,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9940,0.0015,0.0004,0.0017</t>
+  </si>
+  <si>
+    <t>0.9677,0.0201,0.0053,0.0036</t>
+  </si>
+  <si>
+    <t>0.9558,0.0584,0.0035,0.0020</t>
+  </si>
+  <si>
+    <t>0.9832,0.0099,0.0020,0.0022</t>
+  </si>
+  <si>
+    <t>0.0118,0.0034,0.9877,0.0013</t>
+  </si>
+  <si>
+    <t>0.0210,0.0077,0.9740,0.0014</t>
+  </si>
+  <si>
+    <t>0.5370,0.0948,0.1630,0.2832</t>
+  </si>
+  <si>
+    <t>0.1351,0.0227,0.8826,0.0027</t>
+  </si>
+  <si>
+    <t>0.0552,0.9424,0.0147,0.0013</t>
+  </si>
+  <si>
+    <t>0.1220,0.8881,0.0164,0.0028</t>
+  </si>
+  <si>
+    <t>0.0403,0.9563,0.0012,0.0024</t>
+  </si>
+  <si>
+    <t>0.2103,0.8487,0.0070,0.0015</t>
+  </si>
+  <si>
+    <t>0.0234,0.9689,0.0047,0.0019</t>
+  </si>
+  <si>
+    <t>0.0026,0.9952,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.2316,0.8320,0.0066,0.0023</t>
+  </si>
+  <si>
+    <t>0.3070,0.6765,0.0527,0.0414</t>
+  </si>
+  <si>
+    <t>0.1944,0.0613,0.7579,0.0057</t>
+  </si>
+  <si>
+    <t>0.4565,0.3137,0.2841,0.0227</t>
+  </si>
+  <si>
+    <t>0.3416,0.2412,0.5220,0.0258</t>
+  </si>
+  <si>
+    <t>0.0702,0.4961,0.0482,0.8137</t>
+  </si>
+  <si>
+    <t>0.0048,0.9817,0.0192,0.0035</t>
+  </si>
+  <si>
+    <t>0.0041,0.9755,0.0282,0.0073</t>
+  </si>
+  <si>
+    <t>0.0217,0.9461,0.0148,0.0305</t>
+  </si>
+  <si>
+    <t>0.0003,0.9544,0.9236,0.0001</t>
+  </si>
+  <si>
+    <t>0.0056,0.9855,0.0401,0.0003</t>
+  </si>
+  <si>
+    <t>0.3577,0.7600,0.0054,0.0007</t>
+  </si>
+  <si>
+    <t>0.4177,0.6896,0.0047,0.0010</t>
+  </si>
+  <si>
+    <t>0.9762,0.0142,0.0055,0.0020</t>
+  </si>
+  <si>
+    <t>0.9917,0.0019,0.0013,0.0015</t>
+  </si>
+  <si>
+    <t>0.9598,0.0350,0.0052,0.0036</t>
+  </si>
+  <si>
+    <t>0.9599,0.0335,0.0068,0.0035</t>
+  </si>
+  <si>
+    <t>0.9859,0.0075,0.0015,0.0017</t>
+  </si>
+  <si>
+    <t>0.9693,0.0342,0.0051,0.0007</t>
+  </si>
+  <si>
+    <t>0.9761,0.0103,0.0026,0.0041</t>
+  </si>
+  <si>
+    <t>0.9627,0.0309,0.0064,0.0034</t>
+  </si>
+  <si>
+    <t>0.0003,0.6288,0.9873,0.0000</t>
+  </si>
+  <si>
+    <t>0.0077,0.7567,0.7032,0.0006</t>
+  </si>
+  <si>
+    <t>0.0100,0.1673,0.9352,0.0007</t>
+  </si>
+  <si>
+    <t>0.0335,0.1666,0.8762,0.0007</t>
+  </si>
+  <si>
+    <t>0.6776,0.0561,0.2538,0.0463</t>
+  </si>
+  <si>
+    <t>0.6103,0.2578,0.1492,0.0118</t>
+  </si>
+  <si>
+    <t>0.5243,0.0251,0.5346,0.0186</t>
+  </si>
+  <si>
+    <t>0.5172,0.1373,0.4159,0.0355</t>
+  </si>
+  <si>
+    <t>0.0582,0.0042,0.0170,0.9446</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0003,0.9999</t>
+  </si>
+  <si>
+    <t>0.0004,0.0098,0.0012,0.9987</t>
+  </si>
+  <si>
+    <t>0.0051,0.0004,0.0025,0.9954</t>
+  </si>
+  <si>
+    <t>0.0068,0.8753,0.6433,0.0032</t>
+  </si>
+  <si>
+    <t>0.9606,0.0162,0.0105,0.0060</t>
+  </si>
+  <si>
+    <t>0.6665,0.4189,0.0087,0.0070</t>
+  </si>
+  <si>
+    <t>0.9672,0.0137,0.0036,0.0097</t>
+  </si>
+  <si>
+    <t>0.6688,0.4282,0.0082,0.0011</t>
+  </si>
+  <si>
+    <t>0.9544,0.0201,0.0057,0.0080</t>
+  </si>
+  <si>
+    <t>0.3085,0.0375,0.0889,0.6892</t>
+  </si>
+  <si>
+    <t>0.9348,0.0122,0.0029,0.0312</t>
+  </si>
+  <si>
+    <t>0.0015,0.1523,0.9811,0.0018</t>
+  </si>
+  <si>
+    <t>0.4402,0.0010,0.0072,0.6379</t>
+  </si>
+  <si>
+    <t>0.8990,0.0047,0.0010,0.0859</t>
+  </si>
+  <si>
+    <t>0.5426,0.1750,0.3431,0.0130</t>
+  </si>
+  <si>
+    <t>0.8703,0.0775,0.0200,0.0187</t>
+  </si>
+  <si>
+    <t>0.8870,0.0516,0.0560,0.0044</t>
+  </si>
+  <si>
+    <t>0.0178,0.9465,0.0119,0.0300</t>
+  </si>
+  <si>
+    <t>0.6015,0.3308,0.1132,0.0083</t>
+  </si>
+  <si>
+    <t>0.6846,0.1684,0.1918,0.0110</t>
+  </si>
+  <si>
+    <t>0.9864,0.0029,0.0016,0.0032</t>
+  </si>
+  <si>
+    <t>0.9757,0.0203,0.0028,0.0021</t>
+  </si>
+  <si>
+    <t>0.9911,0.0025,0.0010,0.0014</t>
+  </si>
+  <si>
+    <t>0.9845,0.0027,0.0020,0.0041</t>
+  </si>
+  <si>
+    <t>0.9897,0.0048,0.0008,0.0012</t>
+  </si>
+  <si>
+    <t>0.9480,0.0423,0.0099,0.0054</t>
+  </si>
+  <si>
+    <t>0.9949,0.0010,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9884,0.0010,0.0002,0.0072</t>
+  </si>
+  <si>
+    <t>0.6203,0.4136,0.0445,0.0107</t>
+  </si>
+  <si>
+    <t>0.7478,0.3185,0.0100,0.0015</t>
+  </si>
+  <si>
+    <t>0.7191,0.3849,0.0064,0.0006</t>
+  </si>
+  <si>
+    <t>0.0745,0.8194,0.2641,0.0078</t>
+  </si>
+  <si>
+    <t>0.9688,0.0275,0.0043,0.0014</t>
+  </si>
+  <si>
+    <t>0.9574,0.0288,0.0057,0.0056</t>
+  </si>
+  <si>
+    <t>0.9770,0.0081,0.0053,0.0022</t>
+  </si>
+  <si>
+    <t>0.6322,0.4899,0.0044,0.0052</t>
+  </si>
+  <si>
+    <t>0.0014,0.0202,0.9954,0.0008</t>
+  </si>
+  <si>
+    <t>0.9434,0.0304,0.0165,0.0055</t>
+  </si>
+  <si>
+    <t>0.0020,0.0104,0.9948,0.0003</t>
+  </si>
+  <si>
+    <t>0.0018,0.0253,0.9878,0.0023</t>
+  </si>
+  <si>
+    <t>0.0785,0.0048,0.9472,0.0036</t>
+  </si>
+  <si>
+    <t>0.0134,0.3602,0.9266,0.0028</t>
+  </si>
+  <si>
+    <t>0.0466,0.0267,0.9482,0.0047</t>
+  </si>
+  <si>
+    <t>0.0117,0.0022,0.9884,0.0010</t>
+  </si>
+  <si>
+    <t>0.0103,0.0024,0.9833,0.0029</t>
+  </si>
+  <si>
+    <t>0.2188,0.2347,0.5939,0.0651</t>
+  </si>
+  <si>
+    <t>0.1964,0.0157,0.8590,0.0021</t>
+  </si>
+  <si>
+    <t>0.3631,0.0905,0.6324,0.0305</t>
+  </si>
+  <si>
+    <t>0.3608,0.1474,0.5440,0.0147</t>
+  </si>
+  <si>
+    <t>0.2816,0.2641,0.5391,0.0250</t>
+  </si>
+  <si>
+    <t>0.2776,0.0389,0.7284,0.0073</t>
+  </si>
+  <si>
+    <t>0.8041,0.0278,0.1397,0.0193</t>
+  </si>
+  <si>
+    <t>0.2617,0.0359,0.7489,0.0183</t>
+  </si>
+  <si>
+    <t>0.6074,0.5320,0.0066,0.0010</t>
+  </si>
+  <si>
+    <t>0.2131,0.8536,0.0047,0.0006</t>
+  </si>
+  <si>
+    <t>0.0264,0.9695,0.0014,0.0015</t>
+  </si>
+  <si>
+    <t>0.8792,0.1923,0.0057,0.0011</t>
+  </si>
+  <si>
+    <t>0.8737,0.1588,0.0156,0.0036</t>
+  </si>
+  <si>
+    <t>0.3001,0.4262,0.2597,0.0219</t>
+  </si>
+  <si>
+    <t>0.8608,0.0433,0.0710,0.0168</t>
+  </si>
+  <si>
+    <t>0.6866,0.0918,0.2110,0.0429</t>
+  </si>
+  <si>
+    <t>0.5474,0.1233,0.3591,0.0190</t>
+  </si>
+  <si>
+    <t>0.4888,0.0339,0.2171,0.2803</t>
+  </si>
+  <si>
+    <t>0.0282,0.0077,0.9693,0.0035</t>
+  </si>
+  <si>
+    <t>0.2260,0.2027,0.6013,0.0573</t>
+  </si>
+  <si>
+    <t>0.0384,0.0447,0.9439,0.0104</t>
+  </si>
+  <si>
+    <t>0.0598,0.0245,0.9371,0.0033</t>
+  </si>
+  <si>
+    <t>0.0314,0.3360,0.8004,0.0047</t>
+  </si>
+  <si>
+    <t>0.9837,0.0042,0.0008,0.0051</t>
+  </si>
+  <si>
+    <t>0.9815,0.0195,0.0017,0.0010</t>
+  </si>
+  <si>
+    <t>0.9857,0.0073,0.0013,0.0019</t>
+  </si>
+  <si>
+    <t>0.9434,0.0560,0.0143,0.0027</t>
+  </si>
+  <si>
+    <t>0.9855,0.0070,0.0017,0.0017</t>
+  </si>
+  <si>
+    <t>0.9906,0.0065,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9892,0.0070,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9710,0.0150,0.0019,0.0055</t>
+  </si>
+  <si>
+    <t>0.2396,0.0111,0.8443,0.0058</t>
+  </si>
+  <si>
+    <t>0.4133,0.1863,0.4630,0.0183</t>
+  </si>
+  <si>
+    <t>0.8448,0.0361,0.0887,0.0261</t>
+  </si>
+  <si>
+    <t>0.0051,0.0076,0.9847,0.0023</t>
+  </si>
+  <si>
+    <t>0.0006,0.0059,0.9973,0.0007</t>
+  </si>
+  <si>
+    <t>0.0306,0.0424,0.9342,0.0064</t>
+  </si>
+  <si>
+    <t>0.0007,0.0064,0.9979,0.0003</t>
+  </si>
+  <si>
+    <t>0.1140,0.0104,0.9139,0.0011</t>
+  </si>
+  <si>
+    <t>0.0008,0.0234,0.9958,0.0006</t>
+  </si>
+  <si>
+    <t>0.0537,0.0237,0.9211,0.0080</t>
+  </si>
+  <si>
+    <t>0.5253,0.0827,0.4288,0.0246</t>
+  </si>
+  <si>
+    <t>0.4974,0.0158,0.5437,0.0180</t>
+  </si>
+  <si>
+    <t>0.6798,0.0123,0.2412,0.0427</t>
+  </si>
+  <si>
+    <t>0.8091,0.0149,0.1306,0.0313</t>
+  </si>
+  <si>
+    <t>0.9830,0.0192,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9686,0.0392,0.0031,0.0015</t>
+  </si>
+  <si>
+    <t>0.9788,0.0085,0.0052,0.0028</t>
+  </si>
+  <si>
+    <t>0.9759,0.0167,0.0027,0.0030</t>
+  </si>
+  <si>
+    <t>0.9851,0.0081,0.0011,0.0022</t>
+  </si>
+  <si>
+    <t>0.9944,0.0033,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9838,0.0144,0.0015,0.0010</t>
+  </si>
+  <si>
+    <t>0.9859,0.0049,0.0005,0.0042</t>
+  </si>
+  <si>
+    <t>0.2349,0.0450,0.7630,0.0018</t>
+  </si>
+  <si>
+    <t>0.0049,0.0095,0.9868,0.0035</t>
+  </si>
+  <si>
+    <t>0.0239,0.0654,0.9584,0.0011</t>
+  </si>
+  <si>
+    <t>0.1357,0.2097,0.7174,0.0104</t>
+  </si>
+  <si>
+    <t>0.0262,0.0072,0.9635,0.0056</t>
+  </si>
+  <si>
+    <t>0.1049,0.0118,0.0434,0.8937</t>
+  </si>
+  <si>
+    <t>0.4960,0.0304,0.4845,0.0327</t>
+  </si>
+  <si>
+    <t>0.0127,0.0219,0.9657,0.0065</t>
+  </si>
+  <si>
+    <t>0.5416,0.0012,0.0038,0.6175</t>
+  </si>
+  <si>
+    <t>0.0079,0.0258,0.0015,0.9934</t>
+  </si>
+  <si>
+    <t>0.0779,0.0493,0.0056,0.9612</t>
+  </si>
+  <si>
+    <t>0.0065,0.0009,0.0013,0.9957</t>
+  </si>
+  <si>
+    <t>0.0070,0.0015,0.0012,0.9957</t>
+  </si>
+  <si>
+    <t>0.8435,0.0729,0.0220,0.0262</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1985,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1999,7 @@
         <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2013,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2069,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2083,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2097,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2125,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2139,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2153,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2167,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2181,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2195,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2209,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2223,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2237,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2251,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2265,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2279,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2293,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2307,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2318,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2335,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2349,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2363,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2374,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2388,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2419,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2433,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2444,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2461,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2486,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2503,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2517,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2531,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2545,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2559,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2584,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2601,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2615,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2629,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2643,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2657,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2671,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2699,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2713,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2741,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2755,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2783,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2797,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2811,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2825,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2839,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2853,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,10 +2864,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2881,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2895,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2920,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2934,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2951,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2965,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2976,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2990,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3007,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3021,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3035,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3049,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3063,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3077,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3091,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3105,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3116,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3133,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3144,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3161,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3175,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3329,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3343,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3371,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3385,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3399,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3413,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3427,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3441,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3455,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3483,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3497,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3511,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3525,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3539,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3550,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3564,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3581,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3592,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3606,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3623,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3637,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3651,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3665,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3679,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3693,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3704,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3718,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3763,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3777,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3791,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3805,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3833,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3847,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3861,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3875,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3889,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3903,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3917,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3928,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3945,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3959,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3973,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3987,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +4001,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4015,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4040,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4068,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4085,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4099,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4127,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4141,7 @@
         <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4155,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4169,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4208,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4309,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4323,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4365,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4379,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4390,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4404,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,10 +4418,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4435,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4449,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4463,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4491,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4547,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4561,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4575,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4589,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4603,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4614,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4628,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4645,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4659,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4670,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4687,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4698,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4712,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4729,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4743,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4757,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4771,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4782,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4799,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4810,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4827,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4838,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4855,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4869,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4883,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4897,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4911,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4953,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4967,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4981,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4995,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5009,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5023,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5048,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5065,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5093,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5107,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5121,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5135,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5149,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5163,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5177,7 @@
         <v>259</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5188,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5205,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5261,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5275,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5289,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5303,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5317,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5331,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5359,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5373,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5387,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5401,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5412,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5426,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5443,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5454,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5471,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5485,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5499,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5513,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5527,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
